--- a/output/Data and Chart Outputs/gb_gas_nts_daily.xlsx
+++ b/output/Data and Chart Outputs/gb_gas_nts_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>GB gas demand by sector (National Gas NTS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -289,7 +290,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -403,6 +404,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>GB gas supply by entry point (National Gas NTS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -536,7 +538,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1049,7 +1051,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-05 03:10 UTC; 1828 days, 2021-10-04 to 2026-10-05</t>
+          <t>2026-10-28 00:39 UTC; 1851 days, 2021-10-04 to 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2298,7 @@
         <v>0.67011</v>
       </c>
       <c r="E61" t="n">
-        <v>10.39008</v>
+        <v>10.39019</v>
       </c>
       <c r="F61" t="n">
         <v>2.43175</v>
@@ -3549,7 +3551,7 @@
         <v>13.94477</v>
       </c>
       <c r="F61" t="n">
-        <v>5.245810000000001</v>
+        <v>4.94012</v>
       </c>
     </row>
   </sheetData>
@@ -3564,7 +3566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1829"/>
+  <dimension ref="A1:T1852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94693,7 +94695,7 @@
         <v>507.83</v>
       </c>
       <c r="L1815" t="n">
-        <v>377.15</v>
+        <v>381.75</v>
       </c>
       <c r="O1815" t="n">
         <v>19.78</v>
@@ -94746,7 +94748,7 @@
         <v>418.87</v>
       </c>
       <c r="L1816" t="n">
-        <v>472.12</v>
+        <v>431.88</v>
       </c>
       <c r="O1816" t="n">
         <v>20.16</v>
@@ -94799,7 +94801,7 @@
         <v>398.14</v>
       </c>
       <c r="L1817" t="n">
-        <v>353.71</v>
+        <v>318.81</v>
       </c>
       <c r="O1817" t="n">
         <v>19.69</v>
@@ -94852,7 +94854,7 @@
         <v>427.59</v>
       </c>
       <c r="L1818" t="n">
-        <v>390.82</v>
+        <v>404.69</v>
       </c>
       <c r="O1818" t="n">
         <v>19.6</v>
@@ -94905,7 +94907,7 @@
         <v>445.99</v>
       </c>
       <c r="L1819" t="n">
-        <v>561.8099999999999</v>
+        <v>496.13</v>
       </c>
       <c r="O1819" t="n">
         <v>19.97</v>
@@ -94958,7 +94960,7 @@
         <v>426.96</v>
       </c>
       <c r="L1820" t="n">
-        <v>267.87</v>
+        <v>233.39</v>
       </c>
       <c r="O1820" t="n">
         <v>19.43</v>
@@ -95011,7 +95013,7 @@
         <v>507.72</v>
       </c>
       <c r="L1821" t="n">
-        <v>205.94</v>
+        <v>167.03</v>
       </c>
       <c r="O1821" t="n">
         <v>19.98</v>
@@ -95064,7 +95066,7 @@
         <v>505.42</v>
       </c>
       <c r="L1822" t="n">
-        <v>490.02</v>
+        <v>447.95</v>
       </c>
       <c r="O1822" t="n">
         <v>20.1</v>
@@ -95117,7 +95119,7 @@
         <v>502.33</v>
       </c>
       <c r="L1823" t="n">
-        <v>145.58</v>
+        <v>108.03</v>
       </c>
       <c r="O1823" t="n">
         <v>19.36</v>
@@ -95152,7 +95154,7 @@
         <v>19.16</v>
       </c>
       <c r="E1824" t="n">
-        <v>358.81</v>
+        <v>358.92</v>
       </c>
       <c r="F1824" t="n">
         <v>259.81</v>
@@ -95170,7 +95172,7 @@
         <v>440.76</v>
       </c>
       <c r="L1824" t="n">
-        <v>51.01</v>
+        <v>20.68</v>
       </c>
       <c r="O1824" t="n">
         <v>18.56</v>
@@ -95196,7 +95198,7 @@
         <v>46296</v>
       </c>
       <c r="B1825" t="n">
-        <v>615.4</v>
+        <v>616.55</v>
       </c>
       <c r="C1825" t="n">
         <v>539.63</v>
@@ -95249,10 +95251,10 @@
         <v>46297</v>
       </c>
       <c r="B1826" t="n">
-        <v>615.99</v>
+        <v>622.41</v>
       </c>
       <c r="C1826" t="n">
-        <v>357.66</v>
+        <v>357.64</v>
       </c>
       <c r="D1826" t="n">
         <v>24.75</v>
@@ -95302,10 +95304,10 @@
         <v>46298</v>
       </c>
       <c r="B1827" t="n">
-        <v>581.6</v>
+        <v>587.6</v>
       </c>
       <c r="C1827" t="n">
-        <v>371.94</v>
+        <v>372</v>
       </c>
       <c r="D1827" t="n">
         <v>32.6</v>
@@ -95327,12 +95329,48 @@
       </c>
       <c r="J1827" t="n">
         <v>398.87</v>
+      </c>
+      <c r="L1827" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O1827" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="P1827" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1827" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R1827" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S1827" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T1827" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1828">
       <c r="A1828" s="4" t="n">
         <v>46299</v>
       </c>
+      <c r="B1828" t="n">
+        <v>630.25</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>288.51</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>260.77</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>604.13</v>
+      </c>
       <c r="G1828" t="n">
         <v>171.23</v>
       </c>
@@ -95344,12 +95382,48 @@
       </c>
       <c r="J1828" t="n">
         <v>539.48</v>
+      </c>
+      <c r="L1828" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="O1828" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="P1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1828" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R1828" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S1828" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T1828" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1829">
       <c r="A1829" s="4" t="n">
         <v>46300</v>
       </c>
+      <c r="B1829" t="n">
+        <v>613.72</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>386.06</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>289.94</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>446.06</v>
+      </c>
       <c r="G1829" t="n">
         <v>161.51</v>
       </c>
@@ -95361,6 +95435,1150 @@
       </c>
       <c r="J1829" t="n">
         <v>485.89</v>
+      </c>
+      <c r="L1829" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="O1829" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="P1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1829" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R1829" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S1829" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T1829" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1830" t="n">
+        <v>685.5</v>
+      </c>
+      <c r="C1830" t="n">
+        <v>647.24</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="H1830" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1830" t="n">
+        <v>786.28</v>
+      </c>
+      <c r="J1830" t="n">
+        <v>516.52</v>
+      </c>
+      <c r="L1830" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="O1830" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="P1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1830" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R1830" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S1830" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T1830" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1831" t="n">
+        <v>805.5599999999999</v>
+      </c>
+      <c r="C1831" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>221.92</v>
+      </c>
+      <c r="G1831" t="n">
+        <v>133.95</v>
+      </c>
+      <c r="H1831" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1831" t="n">
+        <v>732.25</v>
+      </c>
+      <c r="J1831" t="n">
+        <v>477.23</v>
+      </c>
+      <c r="L1831" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="O1831" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="P1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1831" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R1831" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S1831" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T1831" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>944.08</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>130.14</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>155.27</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>147.79</v>
+      </c>
+      <c r="H1832" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1832" t="n">
+        <v>758.28</v>
+      </c>
+      <c r="J1832" t="n">
+        <v>433.21</v>
+      </c>
+      <c r="L1832" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="O1832" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="P1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1832" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="R1832" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S1832" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T1832" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>797.28</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>135.66</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>336.52</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>161.97</v>
+      </c>
+      <c r="H1833" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1833" t="n">
+        <v>705.5700000000001</v>
+      </c>
+      <c r="J1833" t="n">
+        <v>391.41</v>
+      </c>
+      <c r="L1833" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="O1833" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="P1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1833" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R1833" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S1833" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T1833" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>881.22</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>383.57</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="H1834" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1834" t="n">
+        <v>736.86</v>
+      </c>
+      <c r="J1834" t="n">
+        <v>308.06</v>
+      </c>
+      <c r="L1834" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="O1834" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="P1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1834" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R1834" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S1834" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T1834" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1835" t="n">
+        <v>903.9400000000001</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>390.84</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>112.62</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>124.97</v>
+      </c>
+      <c r="H1835" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1835" t="n">
+        <v>783.13</v>
+      </c>
+      <c r="J1835" t="n">
+        <v>394.76</v>
+      </c>
+      <c r="L1835" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="O1835" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="P1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1835" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R1835" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S1835" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T1835" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1836" t="n">
+        <v>891.5599999999999</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>383.42</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>419.03</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>159.97</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="H1836" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1836" t="n">
+        <v>917.89</v>
+      </c>
+      <c r="J1836" t="n">
+        <v>412.74</v>
+      </c>
+      <c r="L1836" t="n">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="O1836" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="P1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1836" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R1836" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S1836" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T1836" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>737.71</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>245.36</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>335.03</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>484.17</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>179.41</v>
+      </c>
+      <c r="H1837" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1837" t="n">
+        <v>816.39</v>
+      </c>
+      <c r="J1837" t="n">
+        <v>478.13</v>
+      </c>
+      <c r="L1837" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="O1837" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="P1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1837" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R1837" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S1837" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T1837" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1838" t="n">
+        <v>870.17</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>283.29</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>23</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>261.85</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>160.35</v>
+      </c>
+      <c r="H1838" t="n">
+        <v>27</v>
+      </c>
+      <c r="I1838" t="n">
+        <v>653.71</v>
+      </c>
+      <c r="J1838" t="n">
+        <v>449.01</v>
+      </c>
+      <c r="L1838" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="O1838" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="P1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1838" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R1838" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S1838" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T1838" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1839" t="n">
+        <v>788.15</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>336.69</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>361.93</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>258.52</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>160.37</v>
+      </c>
+      <c r="H1839" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1839" t="n">
+        <v>746.54</v>
+      </c>
+      <c r="J1839" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="L1839" t="n">
+        <v>125.23</v>
+      </c>
+      <c r="O1839" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="P1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1839" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R1839" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S1839" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T1839" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>894.97</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>247.89</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>163</v>
+      </c>
+      <c r="H1840" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1840" t="n">
+        <v>813.24</v>
+      </c>
+      <c r="J1840" t="n">
+        <v>455.33</v>
+      </c>
+      <c r="L1840" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="O1840" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="P1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1840" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R1840" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S1840" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T1840" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1841" t="n">
+        <v>1062.96</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>129.08</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>286.47</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>264.6</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>170.7</v>
+      </c>
+      <c r="H1841" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1841" t="n">
+        <v>768.97</v>
+      </c>
+      <c r="J1841" t="n">
+        <v>382.71</v>
+      </c>
+      <c r="L1841" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="O1841" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="P1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1841" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R1841" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S1841" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T1841" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1842" t="n">
+        <v>1126.14</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>253.44</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>313.93</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>170.75</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1842" t="n">
+        <v>848.92</v>
+      </c>
+      <c r="J1842" t="n">
+        <v>468.68</v>
+      </c>
+      <c r="L1842" t="n">
+        <v>140.23</v>
+      </c>
+      <c r="O1842" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="P1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1842" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R1842" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S1842" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T1842" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1843" t="n">
+        <v>1156.65</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>487.23</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>307.76</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>194.31</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1843" t="n">
+        <v>857.96</v>
+      </c>
+      <c r="J1843" t="n">
+        <v>484.57</v>
+      </c>
+      <c r="L1843" t="n">
+        <v>209.07</v>
+      </c>
+      <c r="O1843" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="P1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1843" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R1843" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S1843" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T1843" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1844" t="n">
+        <v>1177.21</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1844" t="n">
+        <v>774.38</v>
+      </c>
+      <c r="J1844" t="n">
+        <v>436.73</v>
+      </c>
+      <c r="L1844" t="n">
+        <v>143.33</v>
+      </c>
+      <c r="O1844" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="P1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1844" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="R1844" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S1844" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T1844" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1845" t="n">
+        <v>1300.64</v>
+      </c>
+      <c r="C1845" t="n">
+        <v>278.85</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>326.77</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>160.23</v>
+      </c>
+      <c r="H1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1845" t="n">
+        <v>737.11</v>
+      </c>
+      <c r="J1845" t="n">
+        <v>460.81</v>
+      </c>
+      <c r="L1845" t="n">
+        <v>212.09</v>
+      </c>
+      <c r="O1845" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="P1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1845" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R1845" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S1845" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T1845" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1846" t="n">
+        <v>1261.12</v>
+      </c>
+      <c r="C1846" t="n">
+        <v>279.82</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>286.46</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>158.7</v>
+      </c>
+      <c r="H1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1846" t="n">
+        <v>499.35</v>
+      </c>
+      <c r="J1846" t="n">
+        <v>462.89</v>
+      </c>
+      <c r="L1846" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="O1846" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="P1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1846" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R1846" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S1846" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T1846" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1847" t="n">
+        <v>1400.79</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>194.26</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>243.88</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>135.86</v>
+      </c>
+      <c r="H1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1847" t="n">
+        <v>757.58</v>
+      </c>
+      <c r="J1847" t="n">
+        <v>467.55</v>
+      </c>
+      <c r="L1847" t="n">
+        <v>179.51</v>
+      </c>
+      <c r="O1847" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="P1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1847" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R1847" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S1847" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T1847" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1848" t="n">
+        <v>1485.41</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>217.39</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>255.51</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>127.04</v>
+      </c>
+      <c r="H1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1848" t="n">
+        <v>725.3200000000001</v>
+      </c>
+      <c r="J1848" t="n">
+        <v>472.93</v>
+      </c>
+      <c r="L1848" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="O1848" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="P1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1848" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R1848" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S1848" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T1848" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1849" t="n">
+        <v>1319.35</v>
+      </c>
+      <c r="C1849" t="n">
+        <v>186.37</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>234.13</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>171.83</v>
+      </c>
+      <c r="H1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1849" t="n">
+        <v>811.35</v>
+      </c>
+      <c r="J1849" t="n">
+        <v>541.29</v>
+      </c>
+      <c r="L1849" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="O1849" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="P1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1849" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R1849" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S1849" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T1849" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1850" t="n">
+        <v>1316.4</v>
+      </c>
+      <c r="C1850" t="n">
+        <v>250.68</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>240.48</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>161.79</v>
+      </c>
+      <c r="H1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1850" t="n">
+        <v>809.83</v>
+      </c>
+      <c r="J1850" t="n">
+        <v>558.86</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="G1851" t="n">
+        <v>126.37</v>
+      </c>
+      <c r="I1851" t="n">
+        <v>718.53</v>
+      </c>
+      <c r="J1851" t="n">
+        <v>314.26</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="G1852" t="n">
+        <v>146.02</v>
+      </c>
+      <c r="H1852" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1852" t="n">
+        <v>805.35</v>
+      </c>
+      <c r="J1852" t="n">
+        <v>361.4</v>
       </c>
     </row>
   </sheetData>
